--- a/revision-date/issues_list.xlsx
+++ b/revision-date/issues_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,12 +434,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
+          <t>97677e6b-1d06-4466-8849-043df22984c1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Broken link (404): http://geobc.gov.bc.ca/base-mapping/atlas/trim/</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -449,22 +449,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>646dd927-3248-4fc9-970c-abea15f7d304</t>
+          <t>b6621a3c-1700-4015-a359-56b6c7155835</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>Broken link (404): http://geobc.gov.bc.ca/base-mapping/atlas/trim/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>646dd927-3248-4fc9-970c-abea15f7d304</t>
+          <t>c428c9ff-19ed-40ec-82e0-40ab10960364</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -494,27 +494,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>bd461764-55b0-4c63-935a-5e9d1d5a6fed</t>
+          <t>646dd927-3248-4fc9-970c-abea15f7d304</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-itracksept2023 returned status_code=404</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>da040f55-984d-490d-b917-a67856de4bac</t>
+          <t>646dd927-3248-4fc9-970c-abea15f7d304</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-seastars2024 returned status_code=404</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -524,12 +524,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>f409100d-95e4-4933-a927-fdf8d3b83204</t>
+          <t>bd461764-55b0-4c63-935a-5e9d1d5a6fed</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://drive.google.com/open?id=12Spn0fnOC91dLOahgcf94_lrELHvXFX6 returned status_code=404</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-itracksept2023 returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -539,57 +539,57 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
+          <t>2de5b0d2-71b1-4041-bd01-118e9c529dac</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-zooplankton-microscopy-dataset returned status_code=404</t>
+          <t>Tentative dataset should not have a version</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4b04cbfe-71f4-47b4-b028-3fcd24e7cff2</t>
+          <t>2de5b0d2-71b1-4041-bd01-118e9c529dac</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Jenn Burt' in DataCite not found in CKAN record</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4b04cbfe-71f4-47b4-b028-3fcd24e7cff2</t>
+          <t>da040f55-984d-490d-b917-a67856de4bac</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'J. Burt' in CKAN record not found in DataCite</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-seastars2024 returned status_code=404</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4b04cbfe-71f4-47b4-b028-3fcd24e7cff2</t>
+          <t>0ce3ee5b-425b-4eb0-a201-96bdfb795a3f</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related identifier 'https://doi.org/10.25607/OBP-2068' (IsSupplementedBy) in DataCite not found in CKAN</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -599,12 +599,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
+          <t>f409100d-95e4-4933-a927-fdf8d3b83204</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Broken link (404): http://www.env.gov.bc.ca/omfd/reports/Kelp2007-HakaiPass.pdf</t>
+          <t>Invalid Resource URL: https://drive.google.com/open?id=12Spn0fnOC91dLOahgcf94_lrELHvXFX6 returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -614,12 +614,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>c4932b55-1dd8-4f2f-89da-5822056ecc37</t>
+          <t>139df6dd-772b-424f-b830-30a5ba6abfc6</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Broken link (404): https://doi.org/10.21966/ekwk-r335</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-zooplankton-microscopy-dataset returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -629,42 +629,42 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
+          <t>4b04cbfe-71f4-47b4-b028-3fcd24e7cff2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Broken link (404): https://github.com/HakaiInstitute/hakai-datasets/raw/development/datasets_documents/HakaiWaterPropertiesProfiles/Hakai_Water_Properties_Processing_and_QAQC_Procedure_20210331.pdf</t>
+          <t>Metadata mismatch: creator 'Jenn Burt' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>e4038a43-060b-474e-b6f2-ea68d0081053</t>
+          <t>4b04cbfe-71f4-47b4-b028-3fcd24e7cff2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-calliarthron2023 returned status_code=404</t>
+          <t>Metadata mismatch: author 'J. Burt' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>33bb67af-4d61-4b15-93a9-f3ab2498430b</t>
+          <t>4b04cbfe-71f4-47b4-b028-3fcd24e7cff2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Broken link (404): http://www.env.gov.bc.ca/omfd/reports/Kelp2007-HakaiPass.pdf</t>
+          <t>Metadata mismatch: related identifier 'https://doi.org/10.25607/OBP-2068' (IsSupplementedBy) in DataCite not found in CKAN</t>
         </is>
       </c>
     </row>
@@ -674,12 +674,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>7c2b8668-75a3-4fc8-bff3-bdae5d95f52d</t>
+          <t>0f19ac6e-dc86-445b-b2da-7b61a389222e</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Broken link (404): https://github.com/HakaiInstitute/hakai-qu5-mooring-data</t>
+          <t>Broken link (404): http://www.env.gov.bc.ca/omfd/reports/Kelp2007-HakaiPass.pdf</t>
         </is>
       </c>
     </row>
@@ -689,42 +689,42 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
+          <t>6a28454e-107a-4059-9b7d-e43bf8ee693b</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Metadata mismatch: publication year CKAN='2026' | DataCite='2020'</t>
+          <t>Broken link (500): https://drive.google.com/file/d/1Q_vZwbxk2djrf0uf0YCCQv_NPcBMxFLO/view?usp=drive_link</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
+          <t>c4932b55-1dd8-4f2f-89da-5822056ecc37</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>Broken link (404): https://doi.org/10.21966/ekwk-r335</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
+          <t>1a2aa5c8-9a83-46f7-967d-1127436c2084</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
+          <t>13dc3c6c-9dd4-47a4-92ad-681c653d3565</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1016/j.ecss.2020.107103' in CKAN not found in DataCite</t>
+          <t>Broken link (404): https://github.com/HakaiInstitute/hakai-datasets/raw/development/datasets_documents/HakaiWaterPropertiesProfiles/Hakai_Water_Properties_Processing_and_QAQC_Procedure_20210331.pdf</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
+          <t>e4038a43-060b-474e-b6f2-ea68d0081053</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Broken link (202): https://jakelawlor.shinyapps.io/optimize_ProdVersion/</t>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-wetlab-calliarthron2023 returned status_code=404</t>
         </is>
       </c>
     </row>
@@ -764,12 +764,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
+          <t>33bb67af-4d61-4b15-93a9-f3ab2498430b</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://drive.google.com/open?id=0B3dfJwMwT2k4RzNYOGFUcFNpUms returned status_code=404</t>
+          <t>Broken link (404): http://www.env.gov.bc.ca/omfd/reports/Kelp2007-HakaiPass.pdf</t>
         </is>
       </c>
     </row>
@@ -779,37 +779,37 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
+          <t>7c2b8668-75a3-4fc8-bff3-bdae5d95f52d</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Broken link (202): https://doi.org/10.1109/PACRIM47961.2019.8985053</t>
+          <t>Broken link (404): https://github.com/HakaiInstitute/hakai-qu5-mooring-data</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
+          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Broken link (202): https://doi.org/10.1109/IGARSS.2012.6351194</t>
+          <t>Metadata mismatch: publication year CKAN='2026' | DataCite='2020'</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>bc1133da-5601-4f92-bc53-41be547c936b</t>
+          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -820,11 +820,11 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>bc1133da-5601-4f92-bc53-41be547c936b</t>
+          <t>70f29525-f17b-4bc7-ae7f-d1e7205ba16c</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -839,22 +839,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
+          <t>c035b81c-0fc3-446e-bec5-8b8933ae874b</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
+          <t>ddf1f914-89b7-41fe-8e72-e5217476fc09</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>18911dee-9ca0-408b-8999-28da3e3dde7a</t>
+          <t>d3ed88cb-4f38-4c2e-a966-3dd49c9cafec</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Broken link (connection error): https://www2.gov.bc.ca/gov/content/data/geographic-data-services/topographic-data/freshwater</t>
+          <t>Metadata mismatch: related work '10.1016/j.ecss.2020.107103' in CKAN not found in DataCite</t>
         </is>
       </c>
     </row>
@@ -884,12 +884,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>c7a168e8-f15e-446f-a49d-0b4a1f043ac2</t>
+          <t>c5e60545-c6f2-4945-af0a-21812ba5f0d9</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Broken link (202): https://fjedna.shinyapps.io/census-app1/</t>
+          <t>Broken link (202): https://jakelawlor.shinyapps.io/optimize_ProdVersion/</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>c1e0447b-a06c-44c8-abd0-3108b2f00b7a</t>
+          <t>5216f7f5-a569-4f76-9cab-171f1e847498</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>No version</t>
+          <t>Record DOI HTTPS link is failling: https://doi.org/10.21966/9a97-2j48 status_code=502</t>
         </is>
       </c>
     </row>
@@ -914,12 +914,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>c1e0447b-a06c-44c8-abd0-3108b2f00b7a</t>
+          <t>5216f7f5-a569-4f76-9cab-171f1e847498</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>No DOI defined</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>613ba2f9-b21d-445f-8eaa-f42950c9350b</t>
+          <t>1f4b5991-bbcb-416b-807c-ed8ca5f4d9f4</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-datasets/raw/development/datasets_documents/HakaiWaterPropertiesProfiles/Hakai_Water_Properties_Processing_and_QAQC_Procedure_20210331.pdf returned status_code=404</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -944,102 +944,102 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>b7638e0b-e734-4a96-97af-9e7729b61831</t>
+          <t>def2a409-2319-4e8c-a584-9a467f044ada</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tentative dataset should not have a version</t>
+          <t>Invalid Resource URL: https://drive.google.com/open?id=0B3dfJwMwT2k4RzNYOGFUcFNpUms returned status_code=404</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>b7638e0b-e734-4a96-97af-9e7729b61831</t>
+          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>No funder</t>
+          <t>Broken link (202): https://doi.org/10.1109/PACRIM47961.2019.8985053</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
+          <t>185462b6-5d10-43d8-91b2-b92010e80ff4</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Broken link (202): https://doi.org/10.1109/PACRIM47961.2019.8985053</t>
+          <t>Broken link (202): https://doi.org/10.1109/IGARSS.2012.6351194</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
+          <t>bc1133da-5601-4f92-bc53-41be547c936b</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Broken link (202): https://doi.org/10.1109/IGARSS.2012.6351194</t>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>39818579-9692-4256-9810-d8b80e9821aa</t>
+          <t>bc1133da-5601-4f92-bc53-41be547c936b</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Broken link (500): https://drive.google.com/file/d/1tBYG1Zmw0kxAidpBZglweAv8CXp-H8an/view?usp=sharing</t>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>39818579-9692-4256-9810-d8b80e9821aa</t>
+          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>39818579-9692-4256-9810-d8b80e9821aa</t>
+          <t>49967494-a7b6-4128-b336-671971d1e2c6</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>324c5ae3-b0ac-4302-b701-598ebbb25870</t>
+          <t>1af6a43a-e73b-4774-8e10-b9f2928ab133</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Broken link (502): https://doi.org/10.21966/ywbk-5h57</t>
+          <t>No funder</t>
         </is>
       </c>
     </row>
@@ -1064,27 +1064,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>3fbbd892-55cd-4c96-9669-cecefe726b3f</t>
+          <t>c1e0447b-a06c-44c8-abd0-3108b2f00b7a</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Metadata mismatch: related work '10.1016/j.pocean.2022.102843' in CKAN not found in DataCite</t>
+          <t>No version</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>b01f58f7-1518-4829-aff6-ac4a8f2c0616</t>
+          <t>c1e0447b-a06c-44c8-abd0-3108b2f00b7a</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Broken link (404): https://hakai-segmentation.readthedocs.io/en/latest/</t>
+          <t>No DOI defined</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,252 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>c7a168e8-f15e-446f-a49d-0b4a1f043ac2</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Broken link (202): https://fjedna.shinyapps.io/census-app1/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>0</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>d320d90e-96bf-4993-81c5-f1f57886b0e6</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>No funder</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>0</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>613ba2f9-b21d-445f-8eaa-f42950c9350b</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-datasets/raw/development/datasets_documents/HakaiWaterPropertiesProfiles/Hakai_Water_Properties_Processing_and_QAQC_Procedure_20210331.pdf returned status_code=404</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>0</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>b7638e0b-e734-4a96-97af-9e7729b61831</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>No funder</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>0</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>39818579-9692-4256-9810-d8b80e9821aa</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Metadata mismatch: creator 'Hakai Institute' in DataCite not found in CKAN record</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>1</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>39818579-9692-4256-9810-d8b80e9821aa</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Metadata mismatch: author 'Hakai Geospatial' in CKAN record not found in DataCite</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>0</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>879a98f9-7e86-46dc-9449-e05cbf720b1e</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>No funder</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>0</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Broken link (202): https://doi.org/10.1109/PACRIM47961.2019.8985053</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>1</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>caf810f0-228a-4827-856c-f9b07a2377af</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Broken link (202): https://doi.org/10.1109/IGARSS.2012.6351194</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>0</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>4c7b7347-767d-45e4-b3ad-7e0133b31e1c</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>No funder</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>0</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>8dadb6a8-8eb2-44ea-9d2d-c4332e4c544b</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>No funder</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>0</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>35245eae-e508-47da-bcf7-54346cda086a</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>No funder</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>0</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>5177d019-598e-4415-b778-9688403652c8</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>No funder</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>0</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>3fbbd892-55cd-4c96-9669-cecefe726b3f</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Metadata mismatch: related work '10.1016/j.pocean.2022.102843' in CKAN not found in DataCite</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>0</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>b01f58f7-1518-4829-aff6-ac4a8f2c0616</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Broken link (404): https://hakai-segmentation.readthedocs.io/en/latest/</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>0</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
           <t>acd6c43f-6cbd-43c8-9bff-7d9ae6630295</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>Invalid Resource URL: https://github.com/HakaiInstitute/hakai-datasets/raw/development/datasets_documents/HakaiWaterPropertiesProfiles/Hakai_Water_Properties_Processing_and_QAQC_Procedure_20210331.pdf returned status_code=404</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>0</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>58d56d16-6350-4b01-a062-6bdb2d9f89b4</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Invalid Resource URL: https://www.ncei.noaa.gov/data/oceans/ncei/ocads/data/0276518/ returned status_code=502</t>
         </is>
       </c>
     </row>
